--- a/output/2026-10-01_06_Malesia_Kelantan_Cleaning.xlsx
+++ b/output/2026-10-01_06_Malesia_Kelantan_Cleaning.xlsx
@@ -474,7 +474,6 @@
           <t>Brimax Sdn. Bhd.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -512,7 +511,6 @@
           <t>Sani-Chem Supplies &amp; Services</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -528,7 +526,6 @@
           <t>09-746 2896</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Indirizzo 5169-L, Jalan Kuala Krai, 69382 Kota Bharu. Classificata in directory come 'Cleaning equipment' e tra i fornitori di prodotti chimici/pulizia (businesslist.my).</t>
@@ -536,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -566,7 +563,6 @@
           <t>+6011-6056-2566</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Sede legale/HQ a Pasir Gudang/Kulai, Johor; filiale fisica operativa a No 1K47, Tingkat 1, Kota Bharu City Point, Jalan Ismail Hilir, 15000 Kota Bharu. Distributore B2B prodotti chimici/attrezzature pulizia industriale.</t>
@@ -574,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
